--- a/data/trans_orig/IP1006-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249063</t>
+          <t>249163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250316</t>
+          <t>250312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>502093</t>
+          <t>502044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506961</t>
+          <t>506438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137897</t>
+          <t>136601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265092</t>
+          <t>265466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189434</t>
+          <t>189964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202578</t>
+          <t>202973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394032</t>
+          <t>393306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399486</t>
+          <t>399485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675075</t>
+          <t>675346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680360</t>
+          <t>680379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716410</t>
+          <t>717154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722016</t>
+          <t>722015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394046</t>
+          <t>1394312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401790</t>
+          <t>1401662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141805</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287855</t>
+          <t>287865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>260391</t>
+          <t>260204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266426</t>
+          <t>266428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494206</t>
+          <t>494854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500898</t>
+          <t>500899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151509</t>
+          <t>151393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310630</t>
+          <t>309950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167976</t>
+          <t>168268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171229</t>
+          <t>171334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177303</t>
+          <t>177307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341255</t>
+          <t>341651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348597</t>
+          <t>348629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702839</t>
+          <t>702219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736805</t>
+          <t>736437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>745464</t>
+          <t>745402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1442035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451294</t>
+          <t>1451500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119688</t>
+          <t>120465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252113</t>
+          <t>251738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207859</t>
+          <t>207807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>253600</t>
+          <t>253804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463538</t>
+          <t>463709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>468041</t>
+          <t>468045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185896</t>
+          <t>185474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374438</t>
+          <t>374465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168384</t>
+          <t>167466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341849</t>
+          <t>341820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698133</t>
+          <t>697614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739583</t>
+          <t>739353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744220</t>
+          <t>744218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439745</t>
+          <t>1439610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1447277</t>
+          <t>1447214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1006-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1006-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1165</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4042</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>253071</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252040</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>249163</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>249188</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>253071</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>250312</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>758</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>502044</t>
+          <t>501951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506438</t>
+          <t>506440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3392</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3626</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140795</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138123</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140795</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136601</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>402</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265466</t>
+          <t>265437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1344</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4133</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5322</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205354</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202566</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>192753</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>189964</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>188775</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205354</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202973</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>593</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393306</t>
+          <t>394688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399485</t>
+          <t>399486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5639</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2510</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720600</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>717061</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722016</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>678511</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675346</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680379</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>674610</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680356</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720600</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717154</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722015</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394312</t>
+          <t>1394117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401662</t>
+          <t>1401706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2941</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2929</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>141572</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143929</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141811</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>422</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287865</t>
+          <t>287837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,92 +3012,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2810</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6897</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>264291</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>260032</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>266424</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>264291</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>260204</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>266428</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>704</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>494854</t>
+          <t>494576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500899</t>
+          <t>500900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4086</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3455</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154149</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151393</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151018</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>447</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309950</t>
+          <t>309319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7274</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3069</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3673</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2495</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6623</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175462</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170683</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177302</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170676</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168268</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167664</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>175462</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171334</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177307</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>501</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341651</t>
+          <t>341049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348629</t>
+          <t>348142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11602</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11705</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742253</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>736540</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>745641</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705582</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702219</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702182</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742253</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>736437</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>745402</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2074</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1442035</t>
+          <t>1442091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451500</t>
+          <t>1451219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3699</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123424</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120161</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>123424</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>120465</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251738</t>
+          <t>251050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4564</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4257</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>256802</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>253497</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209981</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>207807</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>207839</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>256802</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>253804</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>709</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463709</t>
+          <t>463697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2979</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188299</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>185474</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>185920</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>534</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374465</t>
+          <t>374475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1537</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5835</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5518</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1537</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171764</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167466</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167783</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>479</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341820</t>
+          <t>342123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6757</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5491</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742845</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738773</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744217</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>701698</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>697614</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703713</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>697458</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703769</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742845</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739353</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744218</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2119</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1439610</t>
+          <t>1440063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1447214</t>
+          <t>1447335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
